--- a/data/feature_mapping_hhs.xlsx
+++ b/data/feature_mapping_hhs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drish\Desktop\hhr\hhs-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078CE08-7642-4A1E-BE1C-9BD3BD36FDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28CDFEC-5BA4-4A1D-9839-4B2E9CDD76A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
   <si>
     <t>Feature</t>
   </si>
@@ -94,9 +94,6 @@
     <t>LVH</t>
   </si>
   <si>
-    <t>Absent = Normal; Present = Risk</t>
-  </si>
-  <si>
     <t>ECG/Echo LVH criteria (ACC/AHA)</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
     <t>Alcohol</t>
   </si>
   <si>
-    <t>None = Normal; Moderate = Borderline; Heavy = Risk</t>
-  </si>
-  <si>
     <t>AHA/NIAAA Alcohol Consumption Guidance</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>Perceived Stress Scale (PSS) Categorization</t>
   </si>
   <si>
-    <t>hs_CRP</t>
-  </si>
-  <si>
     <t>AHA/CDC hs-CRP Cardiovascular Risk Categories</t>
   </si>
   <si>
@@ -241,9 +232,6 @@
     <t>99th Percentile URL, hs-cTn Assay (ng/mL)</t>
   </si>
   <si>
-    <t>CAC_Score</t>
-  </si>
-  <si>
     <t>MESA/SCCT Agatston CAC Risk Categories</t>
   </si>
   <si>
@@ -281,6 +269,27 @@
   </si>
   <si>
     <t>Sex</t>
+  </si>
+  <si>
+    <t>None = Normal; Moderate = Borderline; Occasional= Borderline; Heavy = Risk</t>
+  </si>
+  <si>
+    <t>Resting_Heart_Rate</t>
+  </si>
+  <si>
+    <t>Low=Risk; Moderate=Borderline; High=Normal</t>
+  </si>
+  <si>
+    <t>Low=Normal; Moderate=Borderline; High=Risk</t>
+  </si>
+  <si>
+    <t>Good=Normal; Moderate=Borderline; Poor=Risk</t>
+  </si>
+  <si>
+    <t>CAC</t>
+  </si>
+  <si>
+    <t>hsCRP</t>
   </si>
 </sst>
 </file>
@@ -376,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,6 +409,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -704,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -722,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -749,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -782,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -815,7 +839,7 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -848,7 +872,7 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -881,7 +905,7 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -914,7 +938,7 @@
         <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -947,7 +971,7 @@
         <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -980,7 +1004,7 @@
         <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -1013,7 +1037,7 @@
         <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1030,18 +1054,18 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="K10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -1066,15 +1090,15 @@
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
@@ -1099,15 +1123,15 @@
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1132,15 +1156,15 @@
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
@@ -1165,15 +1189,15 @@
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>11</v>
@@ -1198,15 +1222,15 @@
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
@@ -1231,15 +1255,15 @@
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
@@ -1264,21 +1288,21 @@
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
         <v>29.9</v>
@@ -1297,15 +1321,15 @@
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
@@ -1317,18 +1341,18 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
@@ -1353,15 +1377,15 @@
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
@@ -1386,15 +1410,15 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>11</v>
@@ -1406,18 +1430,18 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K22" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>11</v>
@@ -1442,15 +1466,15 @@
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>11</v>
@@ -1462,18 +1486,18 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="K24" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>11</v>
@@ -1498,15 +1522,15 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>11</v>
@@ -1531,81 +1555,61 @@
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" t="s">
+        <v>85</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="4">
-        <v>150</v>
-      </c>
-      <c r="D27" s="4">
-        <v>300</v>
-      </c>
-      <c r="E27" s="5">
-        <v>60</v>
-      </c>
-      <c r="F27" s="5">
-        <v>150</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
-        <v>60</v>
-      </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="K27" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="4">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4">
-        <v>10</v>
-      </c>
-      <c r="E28" s="5">
-        <v>5</v>
-      </c>
-      <c r="F28" s="5">
-        <v>8</v>
-      </c>
-      <c r="G28" s="6">
-        <v>1</v>
-      </c>
-      <c r="H28" s="6">
-        <v>5</v>
-      </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7" t="s">
+      <c r="K28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="K28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>11</v>
@@ -1617,18 +1621,18 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="7" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>11</v>
@@ -1653,48 +1657,38 @@
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K30" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="4">
-        <v>0</v>
-      </c>
-      <c r="D31" s="4">
-        <v>13</v>
-      </c>
-      <c r="E31" s="5">
-        <v>13</v>
-      </c>
-      <c r="F31" s="5">
-        <v>27</v>
-      </c>
-      <c r="G31" s="6">
-        <v>27</v>
-      </c>
-      <c r="H31" s="6">
-        <v>40</v>
-      </c>
-      <c r="I31" s="7"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="J31" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
@@ -1719,15 +1713,15 @@
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>11</v>
@@ -1752,15 +1746,15 @@
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K33" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>11</v>
@@ -1785,15 +1779,15 @@
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K34" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>11</v>
@@ -1818,15 +1812,15 @@
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K35" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>11</v>
@@ -1851,15 +1845,15 @@
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>11</v>
@@ -1884,15 +1878,15 @@
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>11</v>
@@ -1917,10 +1911,68 @@
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="11">
+        <v>60</v>
+      </c>
+      <c r="D39" s="11">
+        <v>85</v>
+      </c>
+      <c r="E39" s="12">
+        <v>85</v>
+      </c>
+      <c r="F39" s="12">
+        <v>100</v>
+      </c>
+      <c r="G39" s="13">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13">
+        <v>60</v>
+      </c>
+      <c r="K39" t="s">
         <v>80</v>
       </c>
-      <c r="K38" t="s">
-        <v>82</v>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="11">
+        <v>60</v>
+      </c>
+      <c r="D40" s="11">
+        <v>85</v>
+      </c>
+      <c r="E40" s="12">
+        <v>85</v>
+      </c>
+      <c r="F40" s="12">
+        <v>100</v>
+      </c>
+      <c r="G40" s="13">
+        <v>100</v>
+      </c>
+      <c r="H40" s="13">
+        <v>250</v>
+      </c>
+      <c r="K40" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/data/feature_mapping_hhs.xlsx
+++ b/data/feature_mapping_hhs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drish\Desktop\hhr\hhs-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28CDFEC-5BA4-4A1D-9839-4B2E9CDD76A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4820E5A1-5F3E-4F69-AFD4-1387DDDC61A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature_Mapping" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="99">
   <si>
     <t>Feature</t>
   </si>
@@ -290,6 +290,33 @@
   </si>
   <si>
     <t>hsCRP</t>
+  </si>
+  <si>
+    <t>Non_HDL_C</t>
+  </si>
+  <si>
+    <t>Pack_Years</t>
+  </si>
+  <si>
+    <t>Years_Since_Quit</t>
+  </si>
+  <si>
+    <t>Smokeless_Tobacco</t>
+  </si>
+  <si>
+    <t>Genetic_Mutation</t>
+  </si>
+  <si>
+    <t>PRS_Percentile</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>No=Normal; Yes=Risk</t>
+  </si>
+  <si>
+    <t>Absent=Normal; Present= Risk</t>
   </si>
 </sst>
 </file>
@@ -347,7 +374,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -381,11 +408,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -424,6 +460,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -728,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1975,6 +2020,157 @@
         <v>78</v>
       </c>
     </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="11">
+        <v>0</v>
+      </c>
+      <c r="D41" s="11">
+        <v>129</v>
+      </c>
+      <c r="E41" s="12">
+        <v>129</v>
+      </c>
+      <c r="F41" s="12">
+        <v>159</v>
+      </c>
+      <c r="G41" s="13">
+        <v>159</v>
+      </c>
+      <c r="H41" s="13">
+        <v>999</v>
+      </c>
+      <c r="K41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="11">
+        <v>0</v>
+      </c>
+      <c r="D42" s="11">
+        <v>0</v>
+      </c>
+      <c r="E42" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F42" s="12">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G42" s="13">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H42" s="13">
+        <v>999</v>
+      </c>
+      <c r="K42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="11">
+        <v>15</v>
+      </c>
+      <c r="D43" s="11">
+        <v>999</v>
+      </c>
+      <c r="E43" s="12">
+        <v>5</v>
+      </c>
+      <c r="F43" s="12">
+        <v>15</v>
+      </c>
+      <c r="G43" s="13">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13">
+        <v>5</v>
+      </c>
+      <c r="K43" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" t="s">
+        <v>96</v>
+      </c>
+      <c r="I44" t="s">
+        <v>97</v>
+      </c>
+      <c r="K44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="I45" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="11">
+        <v>0</v>
+      </c>
+      <c r="D46" s="11">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="E46" s="14">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="F46" s="15">
+        <v>94.9</v>
+      </c>
+      <c r="G46" s="16">
+        <v>94.9</v>
+      </c>
+      <c r="H46" s="16">
+        <v>100</v>
+      </c>
+      <c r="K46" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/feature_mapping_hhs.xlsx
+++ b/data/feature_mapping_hhs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drish\Desktop\hhr\hhs-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4820E5A1-5F3E-4F69-AFD4-1387DDDC61A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C0DC3F-0CAE-4F59-A91E-A7ABA27D1D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature_Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feature_Mapping!$A$1:$A$46</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="100">
   <si>
     <t>Feature</t>
   </si>
@@ -58,105 +61,54 @@
     <t>Both</t>
   </si>
   <si>
-    <t>BMI</t>
-  </si>
-  <si>
     <t>WHO BMI Classification</t>
   </si>
   <si>
-    <t>Waist_Circumference</t>
-  </si>
-  <si>
     <t>WHO/IDF Abdominal Obesity Thresholds</t>
   </si>
   <si>
-    <t>Waist_Hip_Ratio</t>
-  </si>
-  <si>
     <t>WHO Waist-Hip Ratio Cutoffs</t>
   </si>
   <si>
-    <t>Systolic_BP</t>
-  </si>
-  <si>
     <t>ACC/AHA 2017 Hypertension Guideline</t>
   </si>
   <si>
-    <t>Diastolic_BP</t>
-  </si>
-  <si>
     <t>Pulse_Pressure</t>
   </si>
   <si>
     <t>AHA - Pulse Pressure &amp; Arterial Stiffness</t>
   </si>
   <si>
-    <t>LVH</t>
-  </si>
-  <si>
     <t>ECG/Echo LVH criteria (ACC/AHA)</t>
   </si>
   <si>
-    <t>Total_Cholesterol</t>
-  </si>
-  <si>
     <t>NCEP ATP III</t>
   </si>
   <si>
-    <t>LDL_C</t>
-  </si>
-  <si>
     <t>ACC/AHA Cholesterol Guideline</t>
   </si>
   <si>
-    <t>HDL_C</t>
-  </si>
-  <si>
     <t>NCEP ATP III (higher = healthier)</t>
   </si>
   <si>
-    <t>Triglycerides</t>
-  </si>
-  <si>
-    <t>TC_HDL_Ratio</t>
-  </si>
-  <si>
     <t>AHA Cardiovascular Risk Ratio</t>
   </si>
   <si>
-    <t>ApoB</t>
-  </si>
-  <si>
     <t>ESC/EAS Dyslipidaemia Guideline</t>
   </si>
   <si>
-    <t>Lp_a</t>
-  </si>
-  <si>
     <t>ESC/EAS Consensus on Lp(a) (mg/dL)</t>
   </si>
   <si>
-    <t>Smoking_Status</t>
-  </si>
-  <si>
     <t>Never = Normal; Former = Borderline; Current = Risk</t>
   </si>
   <si>
     <t>AHA Life's Essential 8</t>
   </si>
   <si>
-    <t>Fasting_Glucose</t>
-  </si>
-  <si>
     <t>ADA Diabetes Diagnostic Criteria</t>
   </si>
   <si>
-    <t>HbA1c</t>
-  </si>
-  <si>
-    <t>Diabetes_Status</t>
-  </si>
-  <si>
     <t>No = Normal; Prediabetes = Borderline; Yes = Risk</t>
   </si>
   <si>
@@ -166,54 +118,30 @@
     <t>Widely used HOMA-IR insulin resistance cutoffs</t>
   </si>
   <si>
-    <t>Family_History_CVD</t>
-  </si>
-  <si>
     <t>No = Normal; Yes = Risk</t>
   </si>
   <si>
     <t>ACC/AHA ASCVD Risk Factor</t>
   </si>
   <si>
-    <t>eGFR</t>
-  </si>
-  <si>
     <t>KDIGO CKD Classification (higher = healthier)</t>
   </si>
   <si>
-    <t>UACR</t>
-  </si>
-  <si>
     <t>KDIGO CKD Classification</t>
   </si>
   <si>
-    <t>Physical_Activity</t>
-  </si>
-  <si>
     <t>AHA Life's Essential 8 (higher = healthier)</t>
   </si>
   <si>
-    <t>Dietary_Quality</t>
-  </si>
-  <si>
     <t>AHA Life's Essential 8 Diet Score (higher = healthier)</t>
   </si>
   <si>
-    <t>Alcohol</t>
-  </si>
-  <si>
     <t>AHA/NIAAA Alcohol Consumption Guidance</t>
   </si>
   <si>
-    <t>Sleep_Duration</t>
-  </si>
-  <si>
     <t>AHA Life's Essential 8 Sleep Duration</t>
   </si>
   <si>
-    <t>Perceived_Stress</t>
-  </si>
-  <si>
     <t>Perceived Stress Scale (PSS) Categorization</t>
   </si>
   <si>
@@ -274,9 +202,6 @@
     <t>None = Normal; Moderate = Borderline; Occasional= Borderline; Heavy = Risk</t>
   </si>
   <si>
-    <t>Resting_Heart_Rate</t>
-  </si>
-  <si>
     <t>Low=Risk; Moderate=Borderline; High=Normal</t>
   </si>
   <si>
@@ -286,30 +211,6 @@
     <t>Good=Normal; Moderate=Borderline; Poor=Risk</t>
   </si>
   <si>
-    <t>CAC</t>
-  </si>
-  <si>
-    <t>hsCRP</t>
-  </si>
-  <si>
-    <t>Non_HDL_C</t>
-  </si>
-  <si>
-    <t>Pack_Years</t>
-  </si>
-  <si>
-    <t>Years_Since_Quit</t>
-  </si>
-  <si>
-    <t>Smokeless_Tobacco</t>
-  </si>
-  <si>
-    <t>Genetic_Mutation</t>
-  </si>
-  <si>
-    <t>PRS_Percentile</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -317,6 +218,111 @@
   </si>
   <si>
     <t>Absent=Normal; Present= Risk</t>
+  </si>
+  <si>
+    <t>sbp</t>
+  </si>
+  <si>
+    <t>dpb</t>
+  </si>
+  <si>
+    <t>resting_hr</t>
+  </si>
+  <si>
+    <t>lvh</t>
+  </si>
+  <si>
+    <t>hba1c</t>
+  </si>
+  <si>
+    <t>fasting_glucose</t>
+  </si>
+  <si>
+    <t>diabetes</t>
+  </si>
+  <si>
+    <t>egfr</t>
+  </si>
+  <si>
+    <t>uacr</t>
+  </si>
+  <si>
+    <t>ldl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hdl </t>
+  </si>
+  <si>
+    <t>hdl</t>
+  </si>
+  <si>
+    <t>total_cholestrol</t>
+  </si>
+  <si>
+    <t>non_hdl</t>
+  </si>
+  <si>
+    <t>tc_hdl_ratio</t>
+  </si>
+  <si>
+    <t>triglycerides</t>
+  </si>
+  <si>
+    <t>apob</t>
+  </si>
+  <si>
+    <t>lpa</t>
+  </si>
+  <si>
+    <t>bmi</t>
+  </si>
+  <si>
+    <t>waist</t>
+  </si>
+  <si>
+    <t>whr</t>
+  </si>
+  <si>
+    <t>smoking_status</t>
+  </si>
+  <si>
+    <t>pack_years</t>
+  </si>
+  <si>
+    <t>years_since_quit</t>
+  </si>
+  <si>
+    <t>smokeless_tobacco</t>
+  </si>
+  <si>
+    <t>physical_activity</t>
+  </si>
+  <si>
+    <t>diet_score</t>
+  </si>
+  <si>
+    <t>sleep_hours</t>
+  </si>
+  <si>
+    <t>alcohol_audit</t>
+  </si>
+  <si>
+    <t>stress_score</t>
+  </si>
+  <si>
+    <t>family_history</t>
+  </si>
+  <si>
+    <t>genetic_mutation</t>
+  </si>
+  <si>
+    <t>prs_percentile</t>
+  </si>
+  <si>
+    <t>hscrp</t>
+  </si>
+  <si>
+    <t>cac</t>
   </si>
 </sst>
 </file>
@@ -465,10 +471,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -791,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -818,12 +824,12 @@
         <v>8</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
@@ -848,15 +854,15 @@
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -881,15 +887,15 @@
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -914,15 +920,15 @@
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -947,15 +953,15 @@
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -980,15 +986,15 @@
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>11</v>
@@ -1013,15 +1019,15 @@
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
@@ -1046,15 +1052,15 @@
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>11</v>
@@ -1079,15 +1085,15 @@
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
@@ -1099,18 +1105,18 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -1135,15 +1141,15 @@
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
@@ -1168,15 +1174,15 @@
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1201,15 +1207,15 @@
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
@@ -1234,15 +1240,15 @@
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>11</v>
@@ -1267,15 +1273,15 @@
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
@@ -1300,15 +1306,15 @@
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K16" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
@@ -1333,15 +1339,15 @@
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K17" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
@@ -1366,15 +1372,15 @@
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
@@ -1386,18 +1392,18 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
@@ -1422,15 +1428,15 @@
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K20" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
@@ -1455,15 +1461,15 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K21" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>11</v>
@@ -1475,18 +1481,18 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="7" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K22" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>11</v>
@@ -1511,15 +1517,15 @@
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>11</v>
@@ -1531,18 +1537,18 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>11</v>
@@ -1567,15 +1573,15 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="K25" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>11</v>
@@ -1600,15 +1606,15 @@
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="K26" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>11</v>
@@ -1620,18 +1626,18 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="K27" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>11</v>
@@ -1643,18 +1649,18 @@
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="7" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>11</v>
@@ -1666,18 +1672,18 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="7" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="K29" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>11</v>
@@ -1702,15 +1708,15 @@
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="K30" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>11</v>
@@ -1722,18 +1728,18 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="7" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K31" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
@@ -1758,15 +1764,15 @@
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="K32" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>11</v>
@@ -1791,15 +1797,15 @@
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>11</v>
@@ -1824,15 +1830,15 @@
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="K34" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>11</v>
@@ -1857,15 +1863,15 @@
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="K35" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>11</v>
@@ -1890,15 +1896,15 @@
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="K36" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>11</v>
@@ -1923,15 +1929,15 @@
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="K37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>11</v>
@@ -1956,15 +1962,15 @@
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="K38" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>11</v>
@@ -1988,12 +1994,12 @@
         <v>60</v>
       </c>
       <c r="K39" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>11</v>
@@ -2017,12 +2023,12 @@
         <v>250</v>
       </c>
       <c r="K40" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>11</v>
@@ -2046,12 +2052,12 @@
         <v>999</v>
       </c>
       <c r="K41" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>11</v>
@@ -2075,12 +2081,12 @@
         <v>999</v>
       </c>
       <c r="K42" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>11</v>
@@ -2104,12 +2110,12 @@
         <v>5</v>
       </c>
       <c r="K43" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>11</v>
@@ -2117,18 +2123,18 @@
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="I44" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="K44" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>11</v>
@@ -2136,15 +2142,15 @@
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="I45" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="K45" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>11</v>
@@ -2168,10 +2174,11 @@
         <v>100</v>
       </c>
       <c r="K46" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/feature_mapping_hhs.xlsx
+++ b/data/feature_mapping_hhs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drish\Desktop\hhr\hhs-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C0DC3F-0CAE-4F59-A91E-A7ABA27D1D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EAA8DB-4596-4269-8D76-5A0E0AB32B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="98">
   <si>
     <t>Feature</t>
   </si>
@@ -109,9 +109,6 @@
     <t>ADA Diabetes Diagnostic Criteria</t>
   </si>
   <si>
-    <t>No = Normal; Prediabetes = Borderline; Yes = Risk</t>
-  </si>
-  <si>
     <t>HOMA_IR</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>Low=Normal; Moderate=Borderline; High=Risk</t>
   </si>
   <si>
-    <t>Good=Normal; Moderate=Borderline; Poor=Risk</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>sbp</t>
   </si>
   <si>
-    <t>dpb</t>
-  </si>
-  <si>
     <t>resting_hr</t>
   </si>
   <si>
@@ -256,9 +247,6 @@
     <t>hdl</t>
   </si>
   <si>
-    <t>total_cholestrol</t>
-  </si>
-  <si>
     <t>non_hdl</t>
   </si>
   <si>
@@ -323,6 +311,12 @@
   </si>
   <si>
     <t>cac</t>
+  </si>
+  <si>
+    <t>dbp</t>
+  </si>
+  <si>
+    <t>total_cholesterol</t>
   </si>
 </sst>
 </file>
@@ -797,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -824,12 +818,12 @@
         <v>8</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
@@ -857,12 +851,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -890,12 +884,12 @@
         <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -923,12 +917,12 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -956,12 +950,12 @@
         <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -989,12 +983,12 @@
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>11</v>
@@ -1022,12 +1016,12 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
@@ -1055,7 +1049,7 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -1088,12 +1082,12 @@
         <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
@@ -1105,18 +1099,18 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -1144,12 +1138,12 @@
         <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
@@ -1177,12 +1171,12 @@
         <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1210,12 +1204,12 @@
         <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
@@ -1243,12 +1237,12 @@
         <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>11</v>
@@ -1276,12 +1270,12 @@
         <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
@@ -1309,12 +1303,12 @@
         <v>22</v>
       </c>
       <c r="K16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
@@ -1342,12 +1336,12 @@
         <v>23</v>
       </c>
       <c r="K17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
@@ -1375,12 +1369,12 @@
         <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
@@ -1398,12 +1392,12 @@
         <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
@@ -1431,12 +1425,12 @@
         <v>27</v>
       </c>
       <c r="K20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
@@ -1464,12 +1458,12 @@
         <v>27</v>
       </c>
       <c r="K21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>11</v>
@@ -1481,18 +1475,18 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>11</v>
@@ -1517,15 +1511,15 @@
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>11</v>
@@ -1537,18 +1531,18 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="K24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>11</v>
@@ -1573,15 +1567,15 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>11</v>
@@ -1606,15 +1600,15 @@
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>11</v>
@@ -1626,33 +1620,43 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="7" t="s">
-        <v>61</v>
-      </c>
+      <c r="C28" s="4">
+        <v>20</v>
+      </c>
+      <c r="D28" s="4">
+        <v>44</v>
+      </c>
+      <c r="E28" s="5">
+        <v>44</v>
+      </c>
+      <c r="F28" s="5">
+        <v>70</v>
+      </c>
+      <c r="G28" s="6">
+        <v>70</v>
+      </c>
+      <c r="H28" s="6">
+        <v>95</v>
+      </c>
+      <c r="I28" s="7"/>
       <c r="J28" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K28" t="s">
         <v>54</v>
@@ -1660,7 +1664,7 @@
     </row>
     <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>11</v>
@@ -1672,18 +1676,18 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>11</v>
@@ -1708,15 +1712,15 @@
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>11</v>
@@ -1728,18 +1732,18 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
@@ -1764,15 +1768,15 @@
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>11</v>
@@ -1797,15 +1801,15 @@
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>11</v>
@@ -1830,15 +1834,15 @@
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>11</v>
@@ -1863,15 +1867,15 @@
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>11</v>
@@ -1896,15 +1900,15 @@
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>11</v>
@@ -1929,15 +1933,15 @@
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>11</v>
@@ -1962,15 +1966,15 @@
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>11</v>
@@ -1994,12 +1998,12 @@
         <v>60</v>
       </c>
       <c r="K39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>11</v>
@@ -2023,12 +2027,12 @@
         <v>250</v>
       </c>
       <c r="K40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>11</v>
@@ -2052,12 +2056,12 @@
         <v>999</v>
       </c>
       <c r="K41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>11</v>
@@ -2081,12 +2085,12 @@
         <v>999</v>
       </c>
       <c r="K42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>11</v>
@@ -2110,12 +2114,12 @@
         <v>5</v>
       </c>
       <c r="K43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>11</v>
@@ -2123,18 +2127,18 @@
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>11</v>
@@ -2142,15 +2146,15 @@
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="I45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>11</v>
@@ -2174,7 +2178,7 @@
         <v>100</v>
       </c>
       <c r="K46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
